--- a/tutorial/Archivo-Excel.xlsx
+++ b/tutorial/Archivo-Excel.xlsx
@@ -1734,7 +1734,7 @@
   </sheetData>
   <conditionalFormatting sqref="K4:K35">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
-      <formula>SUMPRODUCT((($D$4:$D$16=$K4)+($E$4:$E$16=$K4)+($F$4:$F$16=$K4)+($G$4:$G$16=$K4)+($H$4:$H$16=$K4))*((COUNTIFS($A$4:$A$16,$A$4:$A$16,$B$4:$B$16,$B$4:$B$16,$D$4:$D$16,$K4)&gt;1)+(COUNTIFS($A$4:$A$16,$A$4:$A$16,$B$4:$B$16,$B$4:$B$16,$E$4:$E$16,$K4)&gt;1)+(COUNTIFS($A$4:$A$16,$A$4:$A$16,$B$4:$B$16,$B$4:$B$16,$F$4:$F$16,$K4)&gt;1)+(COUNTIFS($A$4:$A$16,$A$4:$A$16,$B$4:$B$16,$B$4:$B$16,$G$4:$G$16,$K4)&gt;1)+(COUNTIFS($A$4:$A$16,$A$4:$A$16,$B$4:$B$16,$B$4:$B$16,$H$4:$H$16,$K4)&gt;1)))&gt;0</formula>
+      <formula>SUMPRODUCT((($D$4:$D$16=$K4)+($E$4:$E$16=$K4)+($F$4:$F$16=$K4)+($G$4:$G$16=$K4)+($H$4:$H$16=$K4))*((COUNTIFS($A$4:$A$16,$A$4:$A$16,$B$4:$B$16,$B$4:$B$16,$D$4:$D$16,$K4)+COUNTIFS($A$4:$A$16,$A$4:$A$16,$B$4:$B$16,$B$4:$B$16,$E$4:$E$16,$K4)+COUNTIFS($A$4:$A$16,$A$4:$A$16,$B$4:$B$16,$B$4:$B$16,$F$4:$F$16,$K4)+COUNTIFS($A$4:$A$16,$A$4:$A$16,$B$4:$B$16,$B$4:$B$16,$G$4:$G$16,$K4)+COUNTIFS($A$4:$A$16,$A$4:$A$16,$B$4:$B$16,$B$4:$B$16,$H$4:$H$16,$K4))&gt;1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
